--- a/output/pdf_financials_xlsx/SABA.xlsx
+++ b/output/pdf_financials_xlsx/SABA.xlsx
@@ -8577,10 +8577,10 @@
         </is>
       </c>
       <c r="F151" s="5" t="n">
-        <v>0.032645</v>
+        <v>-0.032645</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.032645</v>
+        <v>-0.032645</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SABA.xlsx
+++ b/output/pdf_financials_xlsx/SABA.xlsx
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.030286</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>0.032645</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.971442</v>
+        <v>-1.001728</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>0.032645</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.971442</v>
+        <v>-1.001728</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>9.6e-05</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.175016</v>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>9.6e-05</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.175016</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">

--- a/output/pdf_financials_xlsx/SABA.xlsx
+++ b/output/pdf_financials_xlsx/SABA.xlsx
@@ -1766,13 +1766,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.009658</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.11038</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.498296</v>
+        <v>0.507954</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.096932</v>
@@ -2379,7 +2379,7 @@
         <v>-0.078513</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>-0.152427</v>
+        <v>0.032645</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-0.971442</v>
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.19694</v>
       </c>
     </row>
     <row r="111">
@@ -5986,7 +5986,11 @@
           <t>Accretion 12</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -6494,7 +6498,11 @@
           <t>Shares issued for cash 16</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -6784,7 +6792,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -7220,7 +7232,11 @@
           <t>Shares issued for cash (Note 12)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -7550,7 +7566,11 @@
           <t>Private placement 11</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
